--- a/Product_Source/手推移动式小型龙门架遥控电动升降龙门架工厂仓库装卸搬运龙门吊/手推移动式小型龙门架遥控电动升降龙门架工厂仓库装卸搬运龙门吊.xlsx
+++ b/Product_Source/手推移动式小型龙门架遥控电动升降龙门架工厂仓库装卸搬运龙门吊/手推移动式小型龙门架遥控电动升降龙门架工厂仓库装卸搬运龙门吊.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AA_Project\Enterprise_Web\hntzs\Data\1688\手推移动式小型龙门架遥控电动升降龙门架工厂仓库装卸搬运龙门吊\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AA_Project\Enterprise_Web\hntzs\technological-trappist\Product_Source\手推移动式小型龙门架遥控电动升降龙门架工厂仓库装卸搬运龙门吊\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FD1C1E-C33F-4471-B46B-682F0B1C4A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717EAE80-B704-44CA-8464-E1C274A7D4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>产品规格</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t>价格 | 库存(台)</t>
-  </si>
-  <si>
-    <t>进货数量</t>
   </si>
   <si>
     <t>产品信息电子图册</t>
@@ -401,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
@@ -410,7 +407,7 @@
     <col min="5" max="5" width="13.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -426,36 +423,33 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>4.5</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -464,15 +458,15 @@
         <v>500</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>101</v>
@@ -481,15 +475,15 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>5.5</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>101</v>
@@ -498,15 +492,15 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>101</v>
@@ -515,15 +509,15 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>6.5</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>101</v>
@@ -532,15 +526,15 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>101</v>
